--- a/docs/downloads/11/tbl_cultures_touchees_alaotra_mangabe.xlsx
+++ b/docs/downloads/11/tbl_cultures_touchees_alaotra_mangabe.xlsx
@@ -693,12 +693,6 @@
           <t>Brède</t>
         </is>
       </c>
-      <c r="C19">
-        <v>3</v>
-      </c>
-      <c r="D19">
-        <v>2.1</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -711,12 +705,6 @@
           <t>Carotte</t>
         </is>
       </c>
-      <c r="C20">
-        <v>3</v>
-      </c>
-      <c r="D20">
-        <v>2.1</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -728,12 +716,6 @@
         <is>
           <t>Petits pois</t>
         </is>
-      </c>
-      <c r="C21">
-        <v>3</v>
-      </c>
-      <c r="D21">
-        <v>2.1</v>
       </c>
     </row>
   </sheetData>
